--- a/data/place_1_2026-08.xlsx
+++ b/data/place_1_2026-08.xlsx
@@ -413,61 +413,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Big boxes</t>
+          <t>Великі коробки</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Big pay</t>
+          <t>Малі коробки</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Small boxes</t>
+          <t>Загальна сума за день</t>
         </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Small pay</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Day total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>500</v>
-      </c>
-      <c r="C2" t="n">
-        <v>225</v>
-      </c>
-      <c r="D2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>175</v>
-      </c>
-      <c r="F2" t="n">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
